--- a/data/WP17/WP17_sachgebiete_SPD_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_SPD_zeitreihe.xlsx
@@ -2092,13 +2092,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C7D9CD3-9FE7-41F8-AFAB-17E7A282E695}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C61745E-1288-4EF0-9A97-7FFFE77F7ABA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E3A5C3-D662-4487-9AEA-58F4F52188FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71492140-AF5F-47D9-8398-DDB8A4AC2767}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B866674-04E8-4C31-BBDD-51E16D0F956D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{218A887A-46E8-4C9C-80E3-10356EA01CA7}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_SPD_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_SPD_zeitreihe.xlsx
@@ -50,6 +50,9 @@
     <t xml:space="preserve">Kommunale Angelegenheiten</t>
   </si>
   <si>
+    <t xml:space="preserve">Ausländer, Migranten</t>
+  </si>
+  <si>
     <t xml:space="preserve">Landesregierung</t>
   </si>
   <si>
@@ -62,7 +65,10 @@
     <t xml:space="preserve">Frühkindliche Bildung</t>
   </si>
   <si>
-    <t xml:space="preserve">Ausländer, Migranten</t>
+    <t xml:space="preserve">Öffentlicher Haushalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berufsausbildung</t>
   </si>
   <si>
     <t xml:space="preserve">Arbeitsbedingungen</t>
@@ -71,58 +77,52 @@
     <t xml:space="preserve">Öffentlicher Dienst</t>
   </si>
   <si>
+    <t xml:space="preserve">Informationsgesellschaft, Medien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allgemeinbildende Schulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wohnungswesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wald, Forsten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programme der EU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirtschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsmarkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideologien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinder, Jugendliche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schadstoffe, Immissionen, Emissionen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europäische Union</t>
+  </si>
+  <si>
     <t xml:space="preserve">Informations- und Kommunikationstechnologien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informationsgesellschaft, Medien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wohnungswesen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allgemeinbildende Schulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehrer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wald, Forsten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Öffentlicher Haushalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programme der EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wirtschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitsmarkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideologien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinder, Jugendliche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schadstoffe, Immissionen, Emissionen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Europäische Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berufsausbildung</t>
   </si>
   <si>
     <t xml:space="preserve">Gesundheitsschutz</t>
@@ -509,13 +509,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -538,13 +538,13 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
@@ -581,13 +581,13 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -598,19 +598,19 @@
         <v>43009</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -624,19 +624,19 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -650,13 +650,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -667,7 +667,7 @@
         <v>43101</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -679,7 +679,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -690,22 +690,22 @@
         <v>43132</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -713,7 +713,7 @@
         <v>43160</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
@@ -722,10 +722,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
@@ -736,19 +736,19 @@
         <v>43191</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
       <c r="E12" t="n">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
@@ -765,13 +765,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -782,19 +782,19 @@
         <v>43252</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -811,7 +811,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -828,7 +828,7 @@
         <v>43313</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -840,7 +840,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -851,13 +851,13 @@
         <v>43344</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
         <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
         <v>66</v>
@@ -874,13 +874,13 @@
         <v>43374</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
@@ -903,7 +903,7 @@
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
         <v>47</v>
@@ -926,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
         <v>8</v>
@@ -943,16 +943,16 @@
         <v>43466</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -975,10 +975,10 @@
         <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -1001,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
         <v>5</v>
@@ -1015,13 +1015,13 @@
         <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
@@ -1064,7 +1064,7 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>6</v>
@@ -1110,16 +1110,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1127,7 +1127,7 @@
         <v>43709</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" t="n">
         <v>6</v>
@@ -1136,13 +1136,13 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1150,22 +1150,22 @@
         <v>43739</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1179,13 +1179,13 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1202,13 +1202,13 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E32" t="n">
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
@@ -1219,13 +1219,13 @@
         <v>43831</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C33" t="n">
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E33" t="n">
         <v>5</v>
@@ -1242,7 +1242,7 @@
         <v>43862</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C34" t="n">
         <v>2</v>
@@ -1254,7 +1254,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -1265,22 +1265,22 @@
         <v>43891</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1300,7 +1300,7 @@
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
@@ -1311,7 +1311,7 @@
         <v>43952</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C37" t="n">
         <v>111</v>
@@ -1340,7 +1340,7 @@
         <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E38" t="n">
         <v>14</v>
@@ -1357,7 +1357,7 @@
         <v>44013</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
         <v>7</v>
@@ -1369,7 +1369,7 @@
         <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
         <v>4</v>
@@ -1403,13 +1403,13 @@
         <v>44075</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
         <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E41" t="n">
         <v>5</v>
@@ -1426,7 +1426,7 @@
         <v>44105</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C42" t="n">
         <v>26</v>
@@ -1461,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
         <v>5</v>
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E44" t="n">
         <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G44" t="n">
         <v>6</v>
@@ -1501,7 +1501,7 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
         <v>9</v>
@@ -1530,7 +1530,7 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G46" t="n">
         <v>8</v>
@@ -1547,13 +1547,13 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" t="n">
         <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G47" t="n">
         <v>8</v>
@@ -1576,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G48" t="n">
         <v>6</v>
@@ -1599,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
         <v>7</v>
@@ -1610,7 +1610,7 @@
         <v>44348</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C50" t="n">
         <v>17</v>
@@ -1633,19 +1633,19 @@
         <v>44378</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" t="n">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E51" t="n">
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G51" t="n">
         <v>9</v>
@@ -1656,19 +1656,19 @@
         <v>44409</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C52" t="n">
         <v>89</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
         <v>88</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G52" t="n">
         <v>6</v>
@@ -1708,13 +1708,13 @@
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1725,7 +1725,7 @@
         <v>44501</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" t="n">
         <v>16</v>
@@ -1737,7 +1737,7 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G55" t="n">
         <v>7</v>
@@ -1748,7 +1748,7 @@
         <v>44531</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C56" t="n">
         <v>12</v>
@@ -1760,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G56" t="n">
         <v>8</v>
@@ -1817,19 +1817,19 @@
         <v>44621</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C59" t="n">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="n">
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G59" t="n">
         <v>4</v>
@@ -1840,13 +1840,13 @@
         <v>44652</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -2092,13 +2092,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C61745E-1288-4EF0-9A97-7FFFE77F7ABA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E954EA1E-150A-4598-AE0C-31E4D9B901AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71492140-AF5F-47D9-8398-DDB8A4AC2767}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F770A84B-54C0-4E7E-89B0-2C749EF2B881}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{218A887A-46E8-4C9C-80E3-10356EA01CA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6001ABEC-C721-464B-BF3A-4A46913D9FAB}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_SPD_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_SPD_zeitreihe.xlsx
@@ -2092,13 +2092,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E954EA1E-150A-4598-AE0C-31E4D9B901AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE7BA6E7-C4DD-4F0C-8D3D-A5085A3F0222}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F770A84B-54C0-4E7E-89B0-2C749EF2B881}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0B48BA-D9AC-4815-9A81-E39E37F94D1C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6001ABEC-C721-464B-BF3A-4A46913D9FAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05210A3C-82F1-4D80-AAFE-63C8220DE920}"/>
 </file>